--- a/artfynd/A 20946-2026 artfynd.xlsx
+++ b/artfynd/A 20946-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82883087</v>
+        <v>70085727</v>
       </c>
       <c r="B2" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>2666</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514621.8311976585</v>
+        <v>514848</v>
       </c>
       <c r="R2" t="n">
-        <v>6544730.790544545</v>
+        <v>6544853</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-05-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,12 +759,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Lövrik barrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Blocksida</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,62 +786,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126030075</v>
+        <v>70085738</v>
       </c>
       <c r="B3" t="n">
-        <v>41262</v>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>215744</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tajgafältmätare</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Heterothera serraria</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lienig &amp; Zeller, 1846)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ämtsätter, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514723</v>
+        <v>514763</v>
       </c>
       <c r="R3" t="n">
-        <v>6544719</v>
+        <v>6544698</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>22:38</t>
+          <t>2017-05-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>01:51</t>
+          <t>2017-09-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,21 +870,267 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Skogsparti med gran, tall, asp och björkar.</t>
+          <t>Barrskog, lövrik</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Block</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>82883087</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ämtsätter, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>514622</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6544731</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-08-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-09-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Lövrik barrskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126030075</v>
+      </c>
+      <c r="B5" t="n">
+        <v>41501</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>215744</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tajgafältmätare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Heterothera serraria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Lienig &amp; Zeller, 1846)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>lampa</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ämtsätter, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>514723</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6544719</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>22:38</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>01:51</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Skogsparti med gran, tall, asp och björkar.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Björn Gunnarsson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Björn Gunnarsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20946-2026 artfynd.xlsx
+++ b/artfynd/A 20946-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70085727</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70085738</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883087</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,8 +1151,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126030075</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>